--- a/filer/17881248_mols.xlsx
+++ b/filer/17881248_mols.xlsx
@@ -4564,13 +4564,13 @@
         <v>7747</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>0</v>
+        <v>2630</v>
       </c>
       <c r="E3" s="16" t="n">
         <v>30960</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>20692</v>
+        <v>75909</v>
       </c>
     </row>
     <row r="4">
@@ -7004,7 +7004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7150,24 +7150,24 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnDisposalsOfNoncurrentAssets</t>
+          <t>ifrs-full:Ships</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnDisposalsOfNoncurrentAssets</t>
+          <t>ifrs-full:Ships</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n">
-        <v>2630</v>
+        <v>2455952</v>
       </c>
       <c r="G5" s="35" t="n">
-        <v>165</v>
+        <v>2562469</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>55217</v>
+        <v>2375372</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7183,57 +7183,24 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:Ships</t>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:Ships</t>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n">
-        <v>2455952</v>
-      </c>
+      <c r="F6" s="38" t="n"/>
       <c r="G6" s="38" t="n">
-        <v>2562469</v>
+        <v>16159</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>2375372</v>
+        <v>108896</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n">
-        <v>16159</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>108896</v>
-      </c>
-      <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/17881248_mols.xlsx
+++ b/filer/17881248_mols.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/17881248_mols.xlsx
+++ b/filer/17881248_mols.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_17881248" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_17881248" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_17881248" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_17881248" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2721,35 +2722,35 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
@@ -4055,19 +4056,19 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
@@ -4173,19 +4174,19 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
@@ -4482,6 +4483,148 @@
       </c>
       <c r="F92" s="13">
         <f>IFERROR($F$33/($F$55+$F$61)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw_17881248'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw_17881248'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw_17881248'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw_17881248'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw_17881248'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_17881248'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_17881248'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_17881248'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_17881248'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_17881248'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_17881248'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_17881248'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_17881248'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_17881248'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_17881248'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_17881248'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_17881248'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_17881248'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_17881248'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_17881248'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B99">
+        <f>IF(ABS(('pengestrom_raw_17881248'!$B$2+'pengestrom_raw_17881248'!$B$3+'pengestrom_raw_17881248'!$B$4)-'pengestrom_raw_17881248'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_17881248'!$B$2+'pengestrom_raw_17881248'!$B$3+'pengestrom_raw_17881248'!$B$4)-'pengestrom_raw_17881248'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C99">
+        <f>IF(ABS(('pengestrom_raw_17881248'!$C$2+'pengestrom_raw_17881248'!$C$3+'pengestrom_raw_17881248'!$C$4)-'pengestrom_raw_17881248'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_17881248'!$C$2+'pengestrom_raw_17881248'!$C$3+'pengestrom_raw_17881248'!$C$4)-'pengestrom_raw_17881248'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D99">
+        <f>IF(ABS(('pengestrom_raw_17881248'!$D$2+'pengestrom_raw_17881248'!$D$3+'pengestrom_raw_17881248'!$D$4)-'pengestrom_raw_17881248'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_17881248'!$D$2+'pengestrom_raw_17881248'!$D$3+'pengestrom_raw_17881248'!$D$4)-'pengestrom_raw_17881248'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E99">
+        <f>IF(ABS(('pengestrom_raw_17881248'!$E$2+'pengestrom_raw_17881248'!$E$3+'pengestrom_raw_17881248'!$E$4)-'pengestrom_raw_17881248'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_17881248'!$E$2+'pengestrom_raw_17881248'!$E$3+'pengestrom_raw_17881248'!$E$4)-'pengestrom_raw_17881248'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F99">
+        <f>IF(ABS(('pengestrom_raw_17881248'!$F$2+'pengestrom_raw_17881248'!$F$3+'pengestrom_raw_17881248'!$F$4)-'pengestrom_raw_17881248'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_17881248'!$F$2+'pengestrom_raw_17881248'!$F$3+'pengestrom_raw_17881248'!$F$4)-'pengestrom_raw_17881248'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4514,357 +4657,357 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1613036</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1641478</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>2047477</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>2133489</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>2249682</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>2286154</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>60742</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>7747</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>2630</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>30960</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>75909</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>32330</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>352018</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>329594</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>363329</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>403452</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>437895</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>402107</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>-364385</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>460632</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>499894</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>534970</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>547180</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>266597</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>-284763</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>353656</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>382881</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>469081</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>456435</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>336949</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>267423</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>249308</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>262949</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>264448</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>271149</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>1098</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>443</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>3330</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>7163</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>8307</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>123495</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>136022</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>150799</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>135561</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>129732</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>109409</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>214552</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>131844</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>98509</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>130718</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>141879</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>170047</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>509</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>242</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>211</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>-93</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>-618</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>214043</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>131602</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>98298</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>130811</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>142497</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>169962</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>758</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>780</v>
       </c>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>16526</v>
       </c>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4895,879 +5038,885 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>295837</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>263564</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>231290</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>199017</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>166744</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>26854</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>3682402</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>3682402</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>3682402</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>3682402</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>3682402</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>26854</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>4200116</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>4143638</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>4087160</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>4030682</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>3974204</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n">
         <v>660546</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>228191</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>394990</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>1381468</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>3669442</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>3678310</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>56540</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>73038</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>84910</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>105973</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>3724392</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>7878556</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>8009467</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>7751429</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>7647581</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>9120825</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>79778</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>92931</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>109648</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>137502</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>116993</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>113559</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n">
         <v>15735</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>22764</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>28039</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>35532</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>96402</v>
-      </c>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>78427</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>51793</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>36718</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>65897</v>
       </c>
+      <c r="F21" s="17" t="n">
+        <v>119396</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>322623</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>436876</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>40516</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>125575</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>280579</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>47372</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>513769</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>625477</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>217692</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>338718</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>600404</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>363138</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>4238161</v>
-      </c>
-      <c r="C25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>8504033</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>8227159</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>8090147</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>8247985</v>
       </c>
+      <c r="F25" s="17" t="n">
+        <v>9483963</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>283333</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>284100</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>283487</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>283487</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>283487</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>283487</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
-        <v>-30255</v>
-      </c>
-      <c r="C30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>49006</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>14842</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>-31961</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>4966</v>
       </c>
+      <c r="F30" s="17" t="n">
+        <v>-31092</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>821248</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>5220436</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>5308747</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>5439558</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>5517052</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>5521765</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
-        <v>1074326</v>
-      </c>
-      <c r="C32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>5553542</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>5607076</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>5691084</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>5805505</v>
       </c>
+      <c r="F32" s="17" t="n">
+        <v>5774160</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>2329</v>
-      </c>
-      <c r="C33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>1963</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>3276</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>3190</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>3072</v>
       </c>
+      <c r="F33" s="17" t="n">
+        <v>3568</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>1663304</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>1323965</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>965884</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>822171</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>791440</v>
       </c>
+      <c r="F36" s="17" t="n">
+        <v>938680</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>2551701</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>2268836</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>1126814</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>1099628</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>1068952</v>
       </c>
+      <c r="F38" s="17" t="n">
+        <v>2284116</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>152227</v>
-      </c>
-      <c r="C42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>284892</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>368600</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>162277</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>166040</v>
       </c>
+      <c r="F42" s="17" t="n">
+        <v>163410</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
-        <v>62812</v>
-      </c>
-      <c r="C43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>74317</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>96884</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>103393</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>141231</v>
       </c>
+      <c r="F43" s="17" t="n">
+        <v>123136</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v>203055</v>
-      </c>
-      <c r="C48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>136335</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>88364</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>138716</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>115121</v>
       </c>
+      <c r="F48" s="17" t="n">
+        <v>227413</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n">
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n">
         <v>42831</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>46673</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>55396</v>
       </c>
+      <c r="F49" s="17" t="n">
+        <v>62949</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>612134</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>681655</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>1493269</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>1299435</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>1373528</v>
       </c>
+      <c r="F50" s="17" t="n">
+        <v>1425687</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
-        <v>3163835</v>
-      </c>
-      <c r="C51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>2950491</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>2620083</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>2399063</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>2442480</v>
       </c>
+      <c r="F51" s="17" t="n">
+        <v>3709803</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>4238161</v>
-      </c>
-      <c r="C52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>8504033</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>8227159</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>8090147</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>8247985</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>9483963</v>
       </c>
     </row>
   </sheetData>
@@ -5776,6 +5925,138 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>373127</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>402102</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>490840</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>620786</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>634958</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-5041436</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-481937</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-521231</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-189530</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-1654543</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>4768482</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-316525</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>115450</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-276252</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>786378</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>100173</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>-396360</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>85059</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>155004</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>-233207</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5806,13 +6087,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6526,7 +6807,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6644,7 +6925,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6820,7 +7101,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -6998,7 +7279,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7043,27 +7324,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7089,15 +7370,17 @@
         </is>
       </c>
       <c r="D3" s="35" t="n"/>
-      <c r="E3" s="35" t="n"/>
+      <c r="E3" s="35" t="n">
+        <v>353656</v>
+      </c>
       <c r="F3" s="35" t="n">
-        <v>353656</v>
+        <v>382881</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>382881</v>
+        <v>469081</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>469081</v>
+        <v>456435</v>
       </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7122,19 +7405,19 @@
         </is>
       </c>
       <c r="D4" s="38" t="n">
-        <v>242</v>
+        <v>676</v>
       </c>
       <c r="E4" s="38" t="n">
-        <v>676</v>
+        <v>107</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="G4" s="38" t="n">
         <v>16</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7159,15 +7442,17 @@
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
+      <c r="E5" s="35" t="n">
+        <v>2455952</v>
+      </c>
       <c r="F5" s="35" t="n">
-        <v>2455952</v>
+        <v>2562469</v>
       </c>
       <c r="G5" s="35" t="n">
-        <v>2562469</v>
+        <v>2375372</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>2375372</v>
+        <v>2830749</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7193,12 +7478,14 @@
       </c>
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
+      <c r="F6" s="38" t="n">
+        <v>16159</v>
+      </c>
       <c r="G6" s="38" t="n">
-        <v>16159</v>
+        <v>108896</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>108896</v>
+        <v>47279</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
